--- a/Desarrollo/ACP/Cronograma/Cronograma-ACP.xlsx
+++ b/Desarrollo/ACP/Cronograma/Cronograma-ACP.xlsx
@@ -14,11 +14,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={34f8eb5e-583e-4ab1-962b-7f77f7731dba}</author>
-    <author>tc={38481884-f244-4215-ad89-9de9d76cd060}</author>
+    <author>tc={a7c7949f-5bac-4c37-a937-b5f4b69e9aad}</author>
+    <author>tc={dc00d015-4b43-4268-ac91-43b20bc8f418}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{34f8eb5e-583e-4ab1-962b-7f77f7731dba}" ref="F27">
+    <comment authorId="0" xr:uid="{a7c7949f-5bac-4c37-a937-b5f4b69e9aad}" ref="F27">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -27,7 +27,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{38481884-f244-4215-ad89-9de9d76cd060}" ref="A1">
+    <comment authorId="1" xr:uid="{dc00d015-4b43-4268-ac91-43b20bc8f418}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -41,7 +41,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="141">
+  <si>
+    <t>m n,,,,,,,</t>
+  </si>
   <si>
     <t>CRONOGRAMA DEL PROYECTO</t>
   </si>
@@ -335,7 +338,7 @@
     <t>Código Backend</t>
   </si>
   <si>
-    <t>ACP-CBE.zip</t>
+    <t>ACP-CBE</t>
   </si>
   <si>
     <t>Desarrollo de interfaz móvil Android</t>
@@ -344,13 +347,13 @@
     <t>Código Frontend</t>
   </si>
   <si>
-    <t>ACP-CFE.zip</t>
+    <t>ACP-CFE</t>
   </si>
   <si>
     <t>Integración de Frontend con APIs</t>
   </si>
   <si>
-    <t>ACP-CPR.zip</t>
+    <t>ACP-CPR</t>
   </si>
   <si>
     <t>Pizarro / Frontend</t>
@@ -362,7 +365,7 @@
     <t>Reporte de pruebas</t>
   </si>
   <si>
-    <t>ACP-QA02.docx</t>
+    <t>ACP-RP.docx</t>
   </si>
   <si>
     <t>Registro de bugs y corrección de errores (Fixes)</t>
@@ -398,7 +401,7 @@
     <t>Aprobación Línea Base 03</t>
   </si>
   <si>
-    <t>Dashboard Consola</t>
+    <t>Reporte de Línea Base 3</t>
   </si>
   <si>
     <t>ACP-LB03.docx</t>
@@ -642,17 +645,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -717,9 +723,6 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -731,6 +734,9 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -777,7 +783,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Luis Bizarro Ortiz" id="{322ed13d-f9b5-4d6d-9fc6-ad1ffb3582be}" providerId="google-sheets"/>
+  <x18tc:person displayName="Luis Bizarro Ortiz" id="{f8a4671b-1404-4268-b02e-de8bf0e68479}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -977,10 +983,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="F27" dT="2026-05-11T08:25:28.00" personId="{322ed13d-f9b5-4d6d-9fc6-ad1ffb3582be}" id="{34f8eb5e-583e-4ab1-962b-7f77f7731dba}" done="1">
+  <x18tc:threadedComment ref="F27" dT="2026-05-11T08:25:28.00" personId="{f8a4671b-1404-4268-b02e-de8bf0e68479}" id="{a7c7949f-5bac-4c37-a937-b5f4b69e9aad}" done="1">
     <x18tc:text xml:space="preserve">xd</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-05-15T04:19:57.00" personId="{322ed13d-f9b5-4d6d-9fc6-ad1ffb3582be}" id="{38481884-f244-4215-ad89-9de9d76cd060}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-05-15T04:19:57.00" personId="{f8a4671b-1404-4268-b02e-de8bf0e68479}" id="{dc00d015-4b43-4268-ac91-43b20bc8f418}" done="0">
     <x18tc:text xml:space="preserve">mmmm</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1006,9 +1012,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -1036,18 +1044,18 @@
       <c r="AF1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1074,18 +1082,18 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1112,92 +1120,92 @@
       <c r="AF3" s="3"/>
     </row>
     <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
+      <c r="C5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1224,18 +1232,18 @@
       <c r="AF6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="12">
+        <v>11</v>
+      </c>
+      <c r="C7" s="13">
         <v>46146.0</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="1"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1262,18 +1270,18 @@
       <c r="AF7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="13">
+        <v>12</v>
+      </c>
+      <c r="C8" s="14">
         <v>46191.0</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="1"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1300,14 +1308,14 @@
       <c r="AF8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="15"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="1"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1334,27 +1342,27 @@
       <c r="AF9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="F10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>18</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1382,26 +1390,26 @@
       <c r="AF10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="20">
+      <c r="E11" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="21">
         <v>46146.0</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <v>46146.0</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <v>1.0</v>
       </c>
       <c r="I11" s="3"/>
@@ -1430,26 +1438,26 @@
       <c r="AF11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="20">
+      <c r="E12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="21">
         <v>46146.0</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <v>46147.0</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="22">
         <v>1.0</v>
       </c>
       <c r="I12" s="3"/>
@@ -1478,26 +1486,26 @@
       <c r="AF12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="20">
+      <c r="E13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="21">
         <v>46147.0</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <v>46147.0</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="22">
         <v>1.0</v>
       </c>
       <c r="I13" s="3"/>
@@ -1526,26 +1534,26 @@
       <c r="AF13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="C14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="20">
+      <c r="E14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="21">
         <v>46147.0</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <v>46147.0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="22">
         <v>1.0</v>
       </c>
       <c r="I14" s="3"/>
@@ -1574,26 +1582,26 @@
       <c r="AF14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="20">
+      <c r="E15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="21">
         <v>46147.0</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <v>46148.0</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="22">
         <v>1.0</v>
       </c>
       <c r="I15" s="3"/>
@@ -1622,26 +1630,26 @@
       <c r="AF15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="4"/>
+      <c r="B16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="20">
+      <c r="E16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="21">
         <v>46148.0</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <v>46148.0</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <v>1.0</v>
       </c>
       <c r="I16" s="3"/>
@@ -1670,26 +1678,26 @@
       <c r="AF16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="C17" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="D17" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="20">
+      <c r="E17" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="21">
         <v>46148.0</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="21">
         <v>46149.0</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="22">
         <v>1.0</v>
       </c>
       <c r="I17" s="3"/>
@@ -1718,26 +1726,26 @@
       <c r="AF17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="4"/>
+      <c r="B18" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>46150.0</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <v>46150.0</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="22">
         <v>1.0</v>
       </c>
       <c r="I18" s="3"/>
@@ -1766,26 +1774,26 @@
       <c r="AF18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="22"/>
-      <c r="B19" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="C19" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="20">
+      <c r="D19" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="21">
         <v>46150.0</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="21">
         <v>46151.0</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="22">
         <v>1.0</v>
       </c>
       <c r="L19" s="3"/>
@@ -1811,26 +1819,26 @@
       <c r="AF19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="20">
+      <c r="E20" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="21">
         <v>46151.0</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="21">
         <v>46151.0</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="22">
         <v>1.0</v>
       </c>
       <c r="L20" s="3"/>
@@ -1856,26 +1864,26 @@
       <c r="AF20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="C21" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="20">
+      <c r="D21" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="21">
         <v>46152.0</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="21">
         <v>46152.0</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="22">
         <v>1.0</v>
       </c>
       <c r="L21" s="3"/>
@@ -1901,26 +1909,26 @@
       <c r="AF21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="20">
+      <c r="D22" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="21">
         <v>46152.0</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="21">
         <v>46153.0</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <v>1.0</v>
       </c>
       <c r="L22" s="3"/>
@@ -1946,26 +1954,26 @@
       <c r="AF22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="22"/>
-      <c r="B23" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="A23" s="23"/>
+      <c r="B23" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="C23" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="20">
+      <c r="D23" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="21">
         <v>46153.0</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="21">
         <v>46153.0</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="22">
         <v>1.0</v>
       </c>
       <c r="I23" s="3"/>
@@ -1994,26 +2002,26 @@
       <c r="AF23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="22"/>
-      <c r="B24" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C24" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="20">
+      <c r="D24" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="21">
         <v>46154.0</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="21">
         <v>46154.0</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="22">
         <v>1.0</v>
       </c>
       <c r="I24" s="3"/>
@@ -2042,26 +2050,26 @@
       <c r="AF24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="22"/>
-      <c r="B25" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="20">
+      <c r="D25" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="21">
         <v>46155.0</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="21">
         <v>46156.0</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="22">
         <v>1.0</v>
       </c>
       <c r="I25" s="3"/>
@@ -2090,18 +2098,18 @@
       <c r="AF25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="22"/>
-      <c r="B26" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="25">
+      <c r="A26" s="23"/>
+      <c r="B26" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="26">
         <v>46156.0</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2128,26 +2136,26 @@
       <c r="AF26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="A27" s="28"/>
+      <c r="B27" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="C27" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="20">
+      <c r="D27" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="21">
         <v>46156.0</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="21">
         <v>46157.0</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="22">
         <v>1.0</v>
       </c>
       <c r="I27" s="3"/>
@@ -2176,26 +2184,26 @@
       <c r="AF27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="22"/>
-      <c r="B28" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="20">
+      <c r="D28" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="21">
         <v>46156.0</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="21">
         <v>46158.0</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="22">
         <v>1.0</v>
       </c>
       <c r="I28" s="3"/>
@@ -2224,26 +2232,26 @@
       <c r="AF28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="22"/>
-      <c r="B29" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="20">
+      <c r="D29" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="21">
         <v>46156.0</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="21">
         <v>46159.0</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="22">
         <v>1.0</v>
       </c>
       <c r="I29" s="3"/>
@@ -2272,27 +2280,27 @@
       <c r="AF29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="22"/>
-      <c r="B30" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="20">
+      <c r="D30" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="21">
         <v>46160.0</v>
       </c>
-      <c r="G30" s="20">
-        <v>46161.0</v>
-      </c>
-      <c r="H30" s="28">
-        <v>0.0</v>
+      <c r="G30" s="21">
+        <v>46162.0</v>
+      </c>
+      <c r="H30" s="22">
+        <v>1.0</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -2320,27 +2328,27 @@
       <c r="AF30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="20">
+      <c r="D31" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="21">
         <v>46160.0</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="21">
         <v>46162.0</v>
       </c>
-      <c r="H31" s="28">
-        <v>0.0</v>
+      <c r="H31" s="22">
+        <v>1.0</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2369,26 +2377,26 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="29"/>
-      <c r="B32" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="19" t="s">
+      <c r="B32" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="C32" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="20">
+      <c r="D32" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="21">
         <v>46162.0</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <v>46163.0</v>
       </c>
-      <c r="H32" s="28">
-        <v>0.0</v>
+      <c r="H32" s="22">
+        <v>1.0</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2417,17 +2425,17 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="29"/>
-      <c r="B33" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="25">
+      <c r="B33" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="26">
         <v>46163.0</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2455,26 +2463,26 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="29"/>
-      <c r="B34" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>93</v>
       </c>
+      <c r="C34" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="D34" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="20">
+        <v>95</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="21">
         <v>46164.0</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <v>46165.0</v>
       </c>
-      <c r="H34" s="28">
-        <v>0.0</v>
+      <c r="H34" s="22">
+        <v>1.0</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -2503,26 +2511,26 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="29"/>
-      <c r="B35" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>96</v>
       </c>
+      <c r="C35" s="20" t="s">
+        <v>97</v>
+      </c>
       <c r="D35" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="20">
+        <v>98</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="21">
         <v>46165.0</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <v>46174.0</v>
       </c>
-      <c r="H35" s="28">
-        <v>0.0</v>
+      <c r="H35" s="22">
+        <v>1.0</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -2551,26 +2559,26 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="29"/>
-      <c r="B36" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="20" t="s">
         <v>99</v>
       </c>
+      <c r="C36" s="20" t="s">
+        <v>100</v>
+      </c>
       <c r="D36" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="20">
+        <v>101</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="21">
         <v>46164.0</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="21">
         <v>46174.0</v>
       </c>
-      <c r="H36" s="28">
-        <v>0.0</v>
+      <c r="H36" s="22">
+        <v>1.0</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -2599,26 +2607,26 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="29"/>
-      <c r="B37" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>99</v>
+      <c r="B37" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="F37" s="20">
+      <c r="E37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="21">
         <v>46175.0</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="21">
         <v>46178.0</v>
       </c>
-      <c r="H37" s="28">
-        <v>0.0</v>
+      <c r="H37" s="22">
+        <v>1.0</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -2647,26 +2655,26 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="31"/>
-      <c r="B38" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="20" t="s">
         <v>105</v>
       </c>
+      <c r="C38" s="20" t="s">
+        <v>106</v>
+      </c>
       <c r="D38" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="20">
+        <v>107</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="21">
         <v>46178.0</v>
       </c>
-      <c r="G38" s="20">
-        <v>46181.0</v>
-      </c>
-      <c r="H38" s="28">
-        <v>0.0</v>
+      <c r="G38" s="21">
+        <v>46182.0</v>
+      </c>
+      <c r="H38" s="22">
+        <v>1.0</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -2683,26 +2691,26 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="29"/>
-      <c r="B39" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>108</v>
       </c>
+      <c r="C39" s="20" t="s">
+        <v>109</v>
+      </c>
       <c r="D39" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E39" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="F39" s="20">
+      <c r="E39" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="21">
         <v>46182.0</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="21">
         <v>46184.0</v>
       </c>
-      <c r="H39" s="28">
-        <v>0.0</v>
+      <c r="H39" s="22">
+        <v>1.0</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -2731,25 +2739,25 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="29"/>
-      <c r="B40" s="19" t="s">
-        <v>111</v>
+      <c r="B40" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="20">
+        <v>114</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="21">
         <v>46188.0</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="21">
         <v>46189.0</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="33">
         <v>0.0</v>
       </c>
       <c r="I40" s="3"/>
@@ -2779,25 +2787,25 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="29"/>
-      <c r="B41" s="19" t="s">
-        <v>114</v>
+      <c r="B41" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E41" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="F41" s="20">
+        <v>104</v>
+      </c>
+      <c r="F41" s="21">
         <v>46190.0</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="21">
         <v>46190.0</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="33">
         <v>0.0</v>
       </c>
       <c r="I41" s="3"/>
@@ -2827,25 +2835,25 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="29"/>
-      <c r="B42" s="19" t="s">
-        <v>117</v>
+      <c r="B42" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F42" s="20">
+        <v>120</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="21">
         <v>46190.0</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="21">
         <v>46190.0</v>
       </c>
-      <c r="H42" s="28">
+      <c r="H42" s="33">
         <v>0.0</v>
       </c>
       <c r="I42" s="3"/>
@@ -2875,25 +2883,25 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="29"/>
-      <c r="B43" s="19" t="s">
-        <v>120</v>
+      <c r="B43" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="F43" s="20">
+        <v>111</v>
+      </c>
+      <c r="F43" s="21">
         <v>46191.0</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="21">
         <v>46191.0</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="33">
         <v>0.0</v>
       </c>
       <c r="I43" s="3"/>
@@ -2923,17 +2931,17 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="29"/>
-      <c r="B44" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" s="25">
+      <c r="B44" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="26">
         <v>46191.0</v>
       </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -3014,7 +3022,7 @@
       <c r="AF46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1"/>
+      <c r="A47" s="4"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -3041,7 +3049,7 @@
       <c r="AF47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="1"/>
+      <c r="A48" s="4"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -3068,7 +3076,7 @@
       <c r="AF48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1"/>
+      <c r="A49" s="4"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -3095,7 +3103,7 @@
       <c r="AF49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1"/>
+      <c r="A50" s="4"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -3122,13 +3130,13 @@
       <c r="AF50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="34"/>
+      <c r="A51" s="4"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="27"/>
+      <c r="K51" s="27"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="35"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
@@ -3149,14 +3157,14 @@
       <c r="AF51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="1"/>
+      <c r="A52" s="4"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="35"/>
+      <c r="D52" s="36"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="1"/>
+      <c r="H52" s="4"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
@@ -3183,14 +3191,14 @@
       <c r="AF52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="1"/>
+      <c r="A53" s="4"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="11"/>
+      <c r="D53" s="12"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="1"/>
+      <c r="H53" s="4"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -3217,14 +3225,14 @@
       <c r="AF53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="1"/>
+      <c r="A54" s="4"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="11"/>
+      <c r="D54" s="12"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="1"/>
+      <c r="H54" s="4"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -3251,14 +3259,14 @@
       <c r="AF54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="1"/>
+      <c r="A55" s="4"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="11"/>
+      <c r="D55" s="12"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="1"/>
+      <c r="H55" s="4"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
@@ -3285,14 +3293,14 @@
       <c r="AF55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="1"/>
+      <c r="A56" s="4"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="11"/>
+      <c r="D56" s="12"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="1"/>
+      <c r="H56" s="4"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -3319,14 +3327,14 @@
       <c r="AF56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1"/>
+      <c r="A57" s="4"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="11"/>
+      <c r="D57" s="12"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="1"/>
+      <c r="H57" s="4"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -3353,14 +3361,14 @@
       <c r="AF57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="1"/>
+      <c r="A58" s="4"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="11"/>
+      <c r="D58" s="12"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="1"/>
+      <c r="H58" s="4"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3387,14 +3395,14 @@
       <c r="AF58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="1"/>
+      <c r="A59" s="4"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="11"/>
+      <c r="D59" s="12"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="1"/>
+      <c r="H59" s="4"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
@@ -3421,14 +3429,14 @@
       <c r="AF59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="1"/>
+      <c r="A60" s="4"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="11"/>
+      <c r="D60" s="12"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="1"/>
+      <c r="H60" s="4"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -3455,14 +3463,14 @@
       <c r="AF60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="1"/>
+      <c r="A61" s="4"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="11"/>
+      <c r="D61" s="12"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="1"/>
+      <c r="H61" s="4"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
@@ -3489,14 +3497,14 @@
       <c r="AF61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="1"/>
+      <c r="A62" s="4"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="11"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="1"/>
+      <c r="H62" s="4"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -3523,14 +3531,14 @@
       <c r="AF62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="1"/>
+      <c r="A63" s="4"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="11"/>
+      <c r="D63" s="12"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="1"/>
+      <c r="H63" s="4"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -3557,14 +3565,14 @@
       <c r="AF63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="1"/>
+      <c r="A64" s="4"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="11"/>
+      <c r="D64" s="12"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="1"/>
+      <c r="H64" s="4"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -3591,14 +3599,14 @@
       <c r="AF64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="1"/>
+      <c r="A65" s="4"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="12"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
-      <c r="H65" s="1"/>
+      <c r="H65" s="4"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
@@ -3625,14 +3633,14 @@
       <c r="AF65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="1"/>
+      <c r="A66" s="4"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="11"/>
+      <c r="D66" s="12"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="1"/>
+      <c r="H66" s="4"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -3659,14 +3667,14 @@
       <c r="AF66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="1"/>
+      <c r="A67" s="4"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="11"/>
+      <c r="D67" s="12"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="1"/>
+      <c r="H67" s="4"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -3693,14 +3701,14 @@
       <c r="AF67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="1"/>
+      <c r="A68" s="4"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="11"/>
+      <c r="D68" s="12"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="1"/>
+      <c r="H68" s="4"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -3727,14 +3735,14 @@
       <c r="AF68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="1"/>
+      <c r="A69" s="4"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="11"/>
+      <c r="D69" s="12"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="1"/>
+      <c r="H69" s="4"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
@@ -3761,14 +3769,14 @@
       <c r="AF69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="1"/>
+      <c r="A70" s="4"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="11"/>
+      <c r="D70" s="12"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="1"/>
+      <c r="H70" s="4"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
@@ -3795,14 +3803,14 @@
       <c r="AF70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="1"/>
+      <c r="A71" s="4"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="11"/>
+      <c r="D71" s="12"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="1"/>
+      <c r="H71" s="4"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
@@ -3829,14 +3837,14 @@
       <c r="AF71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="1"/>
+      <c r="A72" s="4"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="12"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="1"/>
+      <c r="H72" s="4"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
@@ -3863,14 +3871,14 @@
       <c r="AF72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1"/>
+      <c r="A73" s="4"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="11"/>
+      <c r="D73" s="12"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
-      <c r="H73" s="1"/>
+      <c r="H73" s="4"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
@@ -3897,14 +3905,14 @@
       <c r="AF73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="1"/>
+      <c r="A74" s="4"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="11"/>
+      <c r="D74" s="12"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="1"/>
+      <c r="H74" s="4"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
@@ -3931,14 +3939,14 @@
       <c r="AF74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="1"/>
+      <c r="A75" s="4"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="11"/>
+      <c r="D75" s="12"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
-      <c r="H75" s="1"/>
+      <c r="H75" s="4"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
@@ -3965,14 +3973,14 @@
       <c r="AF75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="1"/>
+      <c r="A76" s="4"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="11"/>
+      <c r="D76" s="12"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="1"/>
+      <c r="H76" s="4"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
@@ -3999,14 +4007,14 @@
       <c r="AF76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="1"/>
+      <c r="A77" s="4"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="11"/>
+      <c r="D77" s="12"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="1"/>
+      <c r="H77" s="4"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
@@ -4033,14 +4041,14 @@
       <c r="AF77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="1"/>
+      <c r="A78" s="4"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="11"/>
+      <c r="D78" s="12"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="1"/>
+      <c r="H78" s="4"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -4067,14 +4075,14 @@
       <c r="AF78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="1"/>
+      <c r="A79" s="4"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="11"/>
+      <c r="D79" s="12"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="1"/>
+      <c r="H79" s="4"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -4101,14 +4109,14 @@
       <c r="AF79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="1"/>
+      <c r="A80" s="4"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="11"/>
+      <c r="D80" s="12"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="1"/>
+      <c r="H80" s="4"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
@@ -4135,14 +4143,14 @@
       <c r="AF80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="1"/>
+      <c r="A81" s="4"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="11"/>
+      <c r="D81" s="12"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="1"/>
+      <c r="H81" s="4"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
@@ -4169,14 +4177,14 @@
       <c r="AF81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1"/>
+      <c r="A82" s="4"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="11"/>
+      <c r="D82" s="12"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="1"/>
+      <c r="H82" s="4"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
@@ -4203,14 +4211,14 @@
       <c r="AF82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="1"/>
+      <c r="A83" s="4"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="11"/>
+      <c r="D83" s="12"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="1"/>
+      <c r="H83" s="4"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
@@ -4237,14 +4245,14 @@
       <c r="AF83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="1"/>
+      <c r="A84" s="4"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="11"/>
+      <c r="D84" s="12"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="1"/>
+      <c r="H84" s="4"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -4271,14 +4279,14 @@
       <c r="AF84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="1"/>
+      <c r="A85" s="4"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="11"/>
+      <c r="D85" s="12"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="1"/>
+      <c r="H85" s="4"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
@@ -4305,14 +4313,14 @@
       <c r="AF85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="1"/>
+      <c r="A86" s="4"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="11"/>
+      <c r="D86" s="12"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="1"/>
+      <c r="H86" s="4"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
@@ -4339,14 +4347,14 @@
       <c r="AF86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="1"/>
+      <c r="A87" s="4"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="11"/>
+      <c r="D87" s="12"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="1"/>
+      <c r="H87" s="4"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
@@ -4373,14 +4381,14 @@
       <c r="AF87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="1"/>
+      <c r="A88" s="4"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="11"/>
+      <c r="D88" s="12"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="1"/>
+      <c r="H88" s="4"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
@@ -4407,14 +4415,14 @@
       <c r="AF88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="1"/>
+      <c r="A89" s="4"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="11"/>
+      <c r="D89" s="12"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="1"/>
+      <c r="H89" s="4"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
@@ -4441,14 +4449,14 @@
       <c r="AF89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="1"/>
+      <c r="A90" s="4"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="11"/>
+      <c r="D90" s="12"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="1"/>
+      <c r="H90" s="4"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
@@ -4475,14 +4483,14 @@
       <c r="AF90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="1"/>
+      <c r="A91" s="4"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="11"/>
+      <c r="D91" s="12"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="1"/>
+      <c r="H91" s="4"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
@@ -4509,14 +4517,14 @@
       <c r="AF91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="1"/>
+      <c r="A92" s="4"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="11"/>
+      <c r="D92" s="12"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="1"/>
+      <c r="H92" s="4"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
@@ -4543,14 +4551,14 @@
       <c r="AF92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="1"/>
+      <c r="A93" s="4"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="11"/>
+      <c r="D93" s="12"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="1"/>
+      <c r="H93" s="4"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -4577,14 +4585,14 @@
       <c r="AF93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="1"/>
+      <c r="A94" s="4"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="11"/>
+      <c r="D94" s="12"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="1"/>
+      <c r="H94" s="4"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
@@ -4611,14 +4619,14 @@
       <c r="AF94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="1"/>
+      <c r="A95" s="4"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="11"/>
+      <c r="D95" s="12"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="1"/>
+      <c r="H95" s="4"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
@@ -4645,14 +4653,14 @@
       <c r="AF95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="1"/>
+      <c r="A96" s="4"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="11"/>
+      <c r="D96" s="12"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="1"/>
+      <c r="H96" s="4"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
@@ -4679,14 +4687,14 @@
       <c r="AF96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="1"/>
+      <c r="A97" s="4"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="11"/>
+      <c r="D97" s="12"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="1"/>
+      <c r="H97" s="4"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
@@ -4713,14 +4721,14 @@
       <c r="AF97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="1"/>
+      <c r="A98" s="4"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="11"/>
+      <c r="D98" s="12"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="1"/>
+      <c r="H98" s="4"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
@@ -4747,14 +4755,14 @@
       <c r="AF98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="1"/>
+      <c r="A99" s="4"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="11"/>
+      <c r="D99" s="12"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="1"/>
+      <c r="H99" s="4"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
@@ -4781,14 +4789,14 @@
       <c r="AF99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="1"/>
+      <c r="A100" s="4"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="11"/>
+      <c r="D100" s="12"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="1"/>
+      <c r="H100" s="4"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
@@ -4815,14 +4823,14 @@
       <c r="AF100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="1"/>
+      <c r="A101" s="4"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="11"/>
+      <c r="D101" s="12"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
-      <c r="H101" s="1"/>
+      <c r="H101" s="4"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
@@ -4849,14 +4857,14 @@
       <c r="AF101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="1"/>
+      <c r="A102" s="4"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="11"/>
+      <c r="D102" s="12"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="1"/>
+      <c r="H102" s="4"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
@@ -4883,14 +4891,14 @@
       <c r="AF102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="1"/>
+      <c r="A103" s="4"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="11"/>
+      <c r="D103" s="12"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="1"/>
+      <c r="H103" s="4"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
@@ -4917,14 +4925,14 @@
       <c r="AF103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="1"/>
+      <c r="A104" s="4"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="11"/>
+      <c r="D104" s="12"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="1"/>
+      <c r="H104" s="4"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
@@ -4951,14 +4959,14 @@
       <c r="AF104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="1"/>
+      <c r="A105" s="4"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="11"/>
+      <c r="D105" s="12"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="1"/>
+      <c r="H105" s="4"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
@@ -4985,14 +4993,14 @@
       <c r="AF105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="1"/>
+      <c r="A106" s="4"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="11"/>
+      <c r="D106" s="12"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="1"/>
+      <c r="H106" s="4"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
@@ -5019,14 +5027,14 @@
       <c r="AF106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="1"/>
+      <c r="A107" s="4"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="11"/>
+      <c r="D107" s="12"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="1"/>
+      <c r="H107" s="4"/>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
@@ -5053,14 +5061,14 @@
       <c r="AF107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="1"/>
+      <c r="A108" s="4"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="11"/>
+      <c r="D108" s="12"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="1"/>
+      <c r="H108" s="4"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
@@ -5087,14 +5095,14 @@
       <c r="AF108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="1"/>
+      <c r="A109" s="4"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="11"/>
+      <c r="D109" s="12"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="1"/>
+      <c r="H109" s="4"/>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
@@ -5121,14 +5129,14 @@
       <c r="AF109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="1"/>
+      <c r="A110" s="4"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="11"/>
+      <c r="D110" s="12"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="1"/>
+      <c r="H110" s="4"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
@@ -5155,14 +5163,14 @@
       <c r="AF110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="1"/>
+      <c r="A111" s="4"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="11"/>
+      <c r="D111" s="12"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="1"/>
+      <c r="H111" s="4"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
@@ -5189,14 +5197,14 @@
       <c r="AF111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="1"/>
+      <c r="A112" s="4"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="11"/>
+      <c r="D112" s="12"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="1"/>
+      <c r="H112" s="4"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
@@ -5223,14 +5231,14 @@
       <c r="AF112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="1"/>
+      <c r="A113" s="4"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="11"/>
+      <c r="D113" s="12"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
-      <c r="H113" s="1"/>
+      <c r="H113" s="4"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
@@ -5257,14 +5265,14 @@
       <c r="AF113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="1"/>
+      <c r="A114" s="4"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="11"/>
+      <c r="D114" s="12"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="1"/>
+      <c r="H114" s="4"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
@@ -5291,14 +5299,14 @@
       <c r="AF114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="1"/>
+      <c r="A115" s="4"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="11"/>
+      <c r="D115" s="12"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="1"/>
+      <c r="H115" s="4"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
@@ -5325,14 +5333,14 @@
       <c r="AF115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="1"/>
+      <c r="A116" s="4"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="11"/>
+      <c r="D116" s="12"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
-      <c r="H116" s="1"/>
+      <c r="H116" s="4"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
@@ -5359,14 +5367,14 @@
       <c r="AF116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="1"/>
+      <c r="A117" s="4"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="11"/>
+      <c r="D117" s="12"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="1"/>
+      <c r="H117" s="4"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
@@ -5393,14 +5401,14 @@
       <c r="AF117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="1"/>
+      <c r="A118" s="4"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="11"/>
+      <c r="D118" s="12"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="1"/>
+      <c r="H118" s="4"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
@@ -5427,14 +5435,14 @@
       <c r="AF118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="1"/>
+      <c r="A119" s="4"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="11"/>
+      <c r="D119" s="12"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="1"/>
+      <c r="H119" s="4"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
@@ -5461,14 +5469,14 @@
       <c r="AF119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="1"/>
+      <c r="A120" s="4"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="11"/>
+      <c r="D120" s="12"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="1"/>
+      <c r="H120" s="4"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
@@ -5495,14 +5503,14 @@
       <c r="AF120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="1"/>
+      <c r="A121" s="4"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="11"/>
+      <c r="D121" s="12"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="1"/>
+      <c r="H121" s="4"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
@@ -5529,14 +5537,14 @@
       <c r="AF121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="1"/>
+      <c r="A122" s="4"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="11"/>
+      <c r="D122" s="12"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
-      <c r="H122" s="1"/>
+      <c r="H122" s="4"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
@@ -5563,14 +5571,14 @@
       <c r="AF122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="A123" s="4"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="11"/>
+      <c r="D123" s="12"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="1"/>
+      <c r="H123" s="4"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
@@ -5597,14 +5605,14 @@
       <c r="AF123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="1"/>
+      <c r="A124" s="4"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="11"/>
+      <c r="D124" s="12"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
-      <c r="H124" s="1"/>
+      <c r="H124" s="4"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
@@ -5631,14 +5639,14 @@
       <c r="AF124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="1"/>
+      <c r="A125" s="4"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="11"/>
+      <c r="D125" s="12"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="1"/>
+      <c r="H125" s="4"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
@@ -5665,14 +5673,14 @@
       <c r="AF125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="1"/>
+      <c r="A126" s="4"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="11"/>
+      <c r="D126" s="12"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
-      <c r="H126" s="1"/>
+      <c r="H126" s="4"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
@@ -5699,14 +5707,14 @@
       <c r="AF126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="1"/>
+      <c r="A127" s="4"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="11"/>
+      <c r="D127" s="12"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="1"/>
+      <c r="H127" s="4"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
@@ -5733,14 +5741,14 @@
       <c r="AF127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="1"/>
+      <c r="A128" s="4"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="11"/>
+      <c r="D128" s="12"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
-      <c r="H128" s="1"/>
+      <c r="H128" s="4"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
@@ -5767,14 +5775,14 @@
       <c r="AF128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="1"/>
+      <c r="A129" s="4"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="11"/>
+      <c r="D129" s="12"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="1"/>
+      <c r="H129" s="4"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
@@ -5801,14 +5809,14 @@
       <c r="AF129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="1"/>
+      <c r="A130" s="4"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="11"/>
+      <c r="D130" s="12"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
-      <c r="H130" s="1"/>
+      <c r="H130" s="4"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
@@ -5835,14 +5843,14 @@
       <c r="AF130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="1"/>
+      <c r="A131" s="4"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="11"/>
+      <c r="D131" s="12"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
-      <c r="H131" s="1"/>
+      <c r="H131" s="4"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
@@ -5869,14 +5877,14 @@
       <c r="AF131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="1"/>
+      <c r="A132" s="4"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="11"/>
+      <c r="D132" s="12"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
-      <c r="H132" s="1"/>
+      <c r="H132" s="4"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
@@ -5903,14 +5911,14 @@
       <c r="AF132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="1"/>
+      <c r="A133" s="4"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="11"/>
+      <c r="D133" s="12"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
-      <c r="H133" s="1"/>
+      <c r="H133" s="4"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -5937,14 +5945,14 @@
       <c r="AF133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="1"/>
+      <c r="A134" s="4"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="11"/>
+      <c r="D134" s="12"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
-      <c r="H134" s="1"/>
+      <c r="H134" s="4"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
@@ -5971,14 +5979,14 @@
       <c r="AF134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="1"/>
+      <c r="A135" s="4"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="11"/>
+      <c r="D135" s="12"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="1"/>
+      <c r="H135" s="4"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
@@ -6005,14 +6013,14 @@
       <c r="AF135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="1"/>
+      <c r="A136" s="4"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="11"/>
+      <c r="D136" s="12"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
-      <c r="H136" s="1"/>
+      <c r="H136" s="4"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
@@ -6039,14 +6047,14 @@
       <c r="AF136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="1"/>
+      <c r="A137" s="4"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="11"/>
+      <c r="D137" s="12"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
-      <c r="H137" s="1"/>
+      <c r="H137" s="4"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
@@ -6073,14 +6081,14 @@
       <c r="AF137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="1"/>
+      <c r="A138" s="4"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="11"/>
+      <c r="D138" s="12"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
-      <c r="H138" s="1"/>
+      <c r="H138" s="4"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
@@ -6107,14 +6115,14 @@
       <c r="AF138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="1"/>
+      <c r="A139" s="4"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="11"/>
+      <c r="D139" s="12"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="1"/>
+      <c r="H139" s="4"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
@@ -6141,14 +6149,14 @@
       <c r="AF139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="1"/>
+      <c r="A140" s="4"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="11"/>
+      <c r="D140" s="12"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
-      <c r="H140" s="1"/>
+      <c r="H140" s="4"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
@@ -6175,14 +6183,14 @@
       <c r="AF140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="1"/>
+      <c r="A141" s="4"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="11"/>
+      <c r="D141" s="12"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
-      <c r="H141" s="1"/>
+      <c r="H141" s="4"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
@@ -6209,14 +6217,14 @@
       <c r="AF141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="1"/>
+      <c r="A142" s="4"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="11"/>
+      <c r="D142" s="12"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
-      <c r="H142" s="1"/>
+      <c r="H142" s="4"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
@@ -6243,14 +6251,14 @@
       <c r="AF142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="1"/>
+      <c r="A143" s="4"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="11"/>
+      <c r="D143" s="12"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
-      <c r="H143" s="1"/>
+      <c r="H143" s="4"/>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
@@ -6277,14 +6285,14 @@
       <c r="AF143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="1"/>
+      <c r="A144" s="4"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="11"/>
+      <c r="D144" s="12"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
-      <c r="H144" s="1"/>
+      <c r="H144" s="4"/>
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
@@ -6311,14 +6319,14 @@
       <c r="AF144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="1"/>
+      <c r="A145" s="4"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="11"/>
+      <c r="D145" s="12"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
-      <c r="H145" s="1"/>
+      <c r="H145" s="4"/>
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
@@ -6345,14 +6353,14 @@
       <c r="AF145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="1"/>
+      <c r="A146" s="4"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="11"/>
+      <c r="D146" s="12"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
-      <c r="H146" s="1"/>
+      <c r="H146" s="4"/>
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
@@ -6379,14 +6387,14 @@
       <c r="AF146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="1"/>
+      <c r="A147" s="4"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="11"/>
+      <c r="D147" s="12"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
-      <c r="H147" s="1"/>
+      <c r="H147" s="4"/>
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
@@ -6413,14 +6421,14 @@
       <c r="AF147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="1"/>
+      <c r="A148" s="4"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="11"/>
+      <c r="D148" s="12"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
-      <c r="H148" s="1"/>
+      <c r="H148" s="4"/>
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
@@ -6447,14 +6455,14 @@
       <c r="AF148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="1"/>
+      <c r="A149" s="4"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="11"/>
+      <c r="D149" s="12"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
-      <c r="H149" s="1"/>
+      <c r="H149" s="4"/>
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
@@ -6481,14 +6489,14 @@
       <c r="AF149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="1"/>
+      <c r="A150" s="4"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="11"/>
+      <c r="D150" s="12"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
-      <c r="H150" s="1"/>
+      <c r="H150" s="4"/>
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
@@ -6515,14 +6523,14 @@
       <c r="AF150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="1"/>
+      <c r="A151" s="4"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="11"/>
+      <c r="D151" s="12"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
-      <c r="H151" s="1"/>
+      <c r="H151" s="4"/>
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
@@ -6549,14 +6557,14 @@
       <c r="AF151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="1"/>
+      <c r="A152" s="4"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="11"/>
+      <c r="D152" s="12"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
-      <c r="H152" s="1"/>
+      <c r="H152" s="4"/>
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
@@ -6583,14 +6591,14 @@
       <c r="AF152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="1"/>
+      <c r="A153" s="4"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="11"/>
+      <c r="D153" s="12"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
-      <c r="H153" s="1"/>
+      <c r="H153" s="4"/>
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
@@ -6617,14 +6625,14 @@
       <c r="AF153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="1"/>
+      <c r="A154" s="4"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="11"/>
+      <c r="D154" s="12"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
-      <c r="H154" s="1"/>
+      <c r="H154" s="4"/>
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
@@ -6651,14 +6659,14 @@
       <c r="AF154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="1"/>
+      <c r="A155" s="4"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="11"/>
+      <c r="D155" s="12"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
-      <c r="H155" s="1"/>
+      <c r="H155" s="4"/>
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
@@ -6685,14 +6693,14 @@
       <c r="AF155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="1"/>
+      <c r="A156" s="4"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="11"/>
+      <c r="D156" s="12"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
-      <c r="H156" s="1"/>
+      <c r="H156" s="4"/>
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
@@ -6719,14 +6727,14 @@
       <c r="AF156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="1"/>
+      <c r="A157" s="4"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="11"/>
+      <c r="D157" s="12"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
-      <c r="H157" s="1"/>
+      <c r="H157" s="4"/>
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
@@ -6753,14 +6761,14 @@
       <c r="AF157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="1"/>
+      <c r="A158" s="4"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="11"/>
+      <c r="D158" s="12"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
-      <c r="H158" s="1"/>
+      <c r="H158" s="4"/>
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
@@ -6787,14 +6795,14 @@
       <c r="AF158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="1"/>
+      <c r="A159" s="4"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="11"/>
+      <c r="D159" s="12"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
-      <c r="H159" s="1"/>
+      <c r="H159" s="4"/>
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
@@ -6821,14 +6829,14 @@
       <c r="AF159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="1"/>
+      <c r="A160" s="4"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="11"/>
+      <c r="D160" s="12"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
-      <c r="H160" s="1"/>
+      <c r="H160" s="4"/>
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
@@ -6855,14 +6863,14 @@
       <c r="AF160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="1"/>
+      <c r="A161" s="4"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="11"/>
+      <c r="D161" s="12"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
-      <c r="H161" s="1"/>
+      <c r="H161" s="4"/>
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
@@ -6889,14 +6897,14 @@
       <c r="AF161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="1"/>
+      <c r="A162" s="4"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="11"/>
+      <c r="D162" s="12"/>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
-      <c r="H162" s="1"/>
+      <c r="H162" s="4"/>
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
@@ -6923,14 +6931,14 @@
       <c r="AF162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="1"/>
+      <c r="A163" s="4"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="11"/>
+      <c r="D163" s="12"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
-      <c r="H163" s="1"/>
+      <c r="H163" s="4"/>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
@@ -6957,14 +6965,14 @@
       <c r="AF163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="1"/>
+      <c r="A164" s="4"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="11"/>
+      <c r="D164" s="12"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
-      <c r="H164" s="1"/>
+      <c r="H164" s="4"/>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
@@ -6991,14 +6999,14 @@
       <c r="AF164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="1"/>
+      <c r="A165" s="4"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="11"/>
+      <c r="D165" s="12"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
-      <c r="H165" s="1"/>
+      <c r="H165" s="4"/>
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
@@ -7025,14 +7033,14 @@
       <c r="AF165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="1"/>
+      <c r="A166" s="4"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="11"/>
+      <c r="D166" s="12"/>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
-      <c r="H166" s="1"/>
+      <c r="H166" s="4"/>
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
@@ -7059,14 +7067,14 @@
       <c r="AF166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="1"/>
+      <c r="A167" s="4"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="11"/>
+      <c r="D167" s="12"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
-      <c r="H167" s="1"/>
+      <c r="H167" s="4"/>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
@@ -7093,14 +7101,14 @@
       <c r="AF167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="1"/>
+      <c r="A168" s="4"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="11"/>
+      <c r="D168" s="12"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
-      <c r="H168" s="1"/>
+      <c r="H168" s="4"/>
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
@@ -7127,14 +7135,14 @@
       <c r="AF168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="1"/>
+      <c r="A169" s="4"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="11"/>
+      <c r="D169" s="12"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
-      <c r="H169" s="1"/>
+      <c r="H169" s="4"/>
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
@@ -7161,14 +7169,14 @@
       <c r="AF169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="1"/>
+      <c r="A170" s="4"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="11"/>
+      <c r="D170" s="12"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
-      <c r="H170" s="1"/>
+      <c r="H170" s="4"/>
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
@@ -7195,14 +7203,14 @@
       <c r="AF170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="1"/>
+      <c r="A171" s="4"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="11"/>
+      <c r="D171" s="12"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
-      <c r="H171" s="1"/>
+      <c r="H171" s="4"/>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
@@ -7229,14 +7237,14 @@
       <c r="AF171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="1"/>
+      <c r="A172" s="4"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="11"/>
+      <c r="D172" s="12"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
-      <c r="H172" s="1"/>
+      <c r="H172" s="4"/>
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
@@ -7263,14 +7271,14 @@
       <c r="AF172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="1"/>
+      <c r="A173" s="4"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="11"/>
+      <c r="D173" s="12"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
-      <c r="H173" s="1"/>
+      <c r="H173" s="4"/>
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
@@ -7297,14 +7305,14 @@
       <c r="AF173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="1"/>
+      <c r="A174" s="4"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="11"/>
+      <c r="D174" s="12"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
-      <c r="H174" s="1"/>
+      <c r="H174" s="4"/>
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
@@ -7331,14 +7339,14 @@
       <c r="AF174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="1"/>
+      <c r="A175" s="4"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="11"/>
+      <c r="D175" s="12"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
-      <c r="H175" s="1"/>
+      <c r="H175" s="4"/>
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
@@ -7365,14 +7373,14 @@
       <c r="AF175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="1"/>
+      <c r="A176" s="4"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="11"/>
+      <c r="D176" s="12"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
-      <c r="H176" s="1"/>
+      <c r="H176" s="4"/>
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
@@ -7399,14 +7407,14 @@
       <c r="AF176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="1"/>
+      <c r="A177" s="4"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="11"/>
+      <c r="D177" s="12"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
-      <c r="H177" s="1"/>
+      <c r="H177" s="4"/>
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
@@ -7433,14 +7441,14 @@
       <c r="AF177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="1"/>
+      <c r="A178" s="4"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="11"/>
+      <c r="D178" s="12"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
-      <c r="H178" s="1"/>
+      <c r="H178" s="4"/>
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
@@ -7467,14 +7475,14 @@
       <c r="AF178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="1"/>
+      <c r="A179" s="4"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="11"/>
+      <c r="D179" s="12"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
-      <c r="H179" s="1"/>
+      <c r="H179" s="4"/>
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
@@ -7501,14 +7509,14 @@
       <c r="AF179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="1"/>
+      <c r="A180" s="4"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="11"/>
+      <c r="D180" s="12"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
-      <c r="H180" s="1"/>
+      <c r="H180" s="4"/>
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
@@ -7535,14 +7543,14 @@
       <c r="AF180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="1"/>
+      <c r="A181" s="4"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="11"/>
+      <c r="D181" s="12"/>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
-      <c r="H181" s="1"/>
+      <c r="H181" s="4"/>
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
@@ -7569,14 +7577,14 @@
       <c r="AF181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="1"/>
+      <c r="A182" s="4"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="11"/>
+      <c r="D182" s="12"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
-      <c r="H182" s="1"/>
+      <c r="H182" s="4"/>
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
@@ -7603,14 +7611,14 @@
       <c r="AF182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="1"/>
+      <c r="A183" s="4"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="11"/>
+      <c r="D183" s="12"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
-      <c r="H183" s="1"/>
+      <c r="H183" s="4"/>
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
@@ -7637,14 +7645,14 @@
       <c r="AF183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="1"/>
+      <c r="A184" s="4"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="11"/>
+      <c r="D184" s="12"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
-      <c r="H184" s="1"/>
+      <c r="H184" s="4"/>
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
@@ -7671,14 +7679,14 @@
       <c r="AF184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="1"/>
+      <c r="A185" s="4"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="11"/>
+      <c r="D185" s="12"/>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
-      <c r="H185" s="1"/>
+      <c r="H185" s="4"/>
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
@@ -7705,14 +7713,14 @@
       <c r="AF185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="1"/>
+      <c r="A186" s="4"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="11"/>
+      <c r="D186" s="12"/>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
-      <c r="H186" s="1"/>
+      <c r="H186" s="4"/>
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
@@ -7739,14 +7747,14 @@
       <c r="AF186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="1"/>
+      <c r="A187" s="4"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="11"/>
+      <c r="D187" s="12"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
-      <c r="H187" s="1"/>
+      <c r="H187" s="4"/>
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
@@ -7773,14 +7781,14 @@
       <c r="AF187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="1"/>
+      <c r="A188" s="4"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="11"/>
+      <c r="D188" s="12"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
-      <c r="H188" s="1"/>
+      <c r="H188" s="4"/>
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
@@ -7807,14 +7815,14 @@
       <c r="AF188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="1"/>
+      <c r="A189" s="4"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="11"/>
+      <c r="D189" s="12"/>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
-      <c r="H189" s="1"/>
+      <c r="H189" s="4"/>
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
@@ -7841,14 +7849,14 @@
       <c r="AF189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="1"/>
+      <c r="A190" s="4"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="11"/>
+      <c r="D190" s="12"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
-      <c r="H190" s="1"/>
+      <c r="H190" s="4"/>
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
@@ -7875,14 +7883,14 @@
       <c r="AF190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="1"/>
+      <c r="A191" s="4"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="11"/>
+      <c r="D191" s="12"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
-      <c r="H191" s="1"/>
+      <c r="H191" s="4"/>
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
@@ -7909,14 +7917,14 @@
       <c r="AF191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="1"/>
+      <c r="A192" s="4"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="11"/>
+      <c r="D192" s="12"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
-      <c r="H192" s="1"/>
+      <c r="H192" s="4"/>
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
@@ -7943,14 +7951,14 @@
       <c r="AF192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="1"/>
+      <c r="A193" s="4"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="11"/>
+      <c r="D193" s="12"/>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
-      <c r="H193" s="1"/>
+      <c r="H193" s="4"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
@@ -7977,14 +7985,14 @@
       <c r="AF193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="1"/>
+      <c r="A194" s="4"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="11"/>
+      <c r="D194" s="12"/>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
-      <c r="H194" s="1"/>
+      <c r="H194" s="4"/>
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
@@ -8011,14 +8019,14 @@
       <c r="AF194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="1"/>
+      <c r="A195" s="4"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="11"/>
+      <c r="D195" s="12"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
-      <c r="H195" s="1"/>
+      <c r="H195" s="4"/>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
@@ -8045,14 +8053,14 @@
       <c r="AF195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="1"/>
+      <c r="A196" s="4"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="11"/>
+      <c r="D196" s="12"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
-      <c r="H196" s="1"/>
+      <c r="H196" s="4"/>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
@@ -8079,14 +8087,14 @@
       <c r="AF196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="1"/>
+      <c r="A197" s="4"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="11"/>
+      <c r="D197" s="12"/>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
-      <c r="H197" s="1"/>
+      <c r="H197" s="4"/>
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
@@ -8113,14 +8121,14 @@
       <c r="AF197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="1"/>
+      <c r="A198" s="4"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="11"/>
+      <c r="D198" s="12"/>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
-      <c r="H198" s="1"/>
+      <c r="H198" s="4"/>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
@@ -8147,14 +8155,14 @@
       <c r="AF198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="1"/>
+      <c r="A199" s="4"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="11"/>
+      <c r="D199" s="12"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
-      <c r="H199" s="1"/>
+      <c r="H199" s="4"/>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
@@ -8181,14 +8189,14 @@
       <c r="AF199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="1"/>
+      <c r="A200" s="4"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="11"/>
+      <c r="D200" s="12"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
-      <c r="H200" s="1"/>
+      <c r="H200" s="4"/>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
@@ -8215,14 +8223,14 @@
       <c r="AF200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="1"/>
+      <c r="A201" s="4"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="11"/>
+      <c r="D201" s="12"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
-      <c r="H201" s="1"/>
+      <c r="H201" s="4"/>
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
@@ -8249,14 +8257,14 @@
       <c r="AF201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="1"/>
+      <c r="A202" s="4"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="11"/>
+      <c r="D202" s="12"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
-      <c r="H202" s="1"/>
+      <c r="H202" s="4"/>
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
@@ -8283,14 +8291,14 @@
       <c r="AF202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="1"/>
+      <c r="A203" s="4"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="11"/>
+      <c r="D203" s="12"/>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
-      <c r="H203" s="1"/>
+      <c r="H203" s="4"/>
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
@@ -8317,14 +8325,14 @@
       <c r="AF203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="1"/>
+      <c r="A204" s="4"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="11"/>
+      <c r="D204" s="12"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
-      <c r="H204" s="1"/>
+      <c r="H204" s="4"/>
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
@@ -8351,14 +8359,14 @@
       <c r="AF204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="1"/>
+      <c r="A205" s="4"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="11"/>
+      <c r="D205" s="12"/>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
-      <c r="H205" s="1"/>
+      <c r="H205" s="4"/>
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
@@ -8385,14 +8393,14 @@
       <c r="AF205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="1"/>
+      <c r="A206" s="4"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="11"/>
+      <c r="D206" s="12"/>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
-      <c r="H206" s="1"/>
+      <c r="H206" s="4"/>
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
@@ -8419,14 +8427,14 @@
       <c r="AF206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="1"/>
+      <c r="A207" s="4"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="11"/>
+      <c r="D207" s="12"/>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
-      <c r="H207" s="1"/>
+      <c r="H207" s="4"/>
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
@@ -8453,14 +8461,14 @@
       <c r="AF207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="1"/>
+      <c r="A208" s="4"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="11"/>
+      <c r="D208" s="12"/>
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
-      <c r="H208" s="1"/>
+      <c r="H208" s="4"/>
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
@@ -8487,14 +8495,14 @@
       <c r="AF208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="1"/>
+      <c r="A209" s="4"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="11"/>
+      <c r="D209" s="12"/>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
-      <c r="H209" s="1"/>
+      <c r="H209" s="4"/>
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
@@ -8521,14 +8529,14 @@
       <c r="AF209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="1"/>
+      <c r="A210" s="4"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="11"/>
+      <c r="D210" s="12"/>
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
-      <c r="H210" s="1"/>
+      <c r="H210" s="4"/>
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
@@ -8555,14 +8563,14 @@
       <c r="AF210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="1"/>
+      <c r="A211" s="4"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="11"/>
+      <c r="D211" s="12"/>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
-      <c r="H211" s="1"/>
+      <c r="H211" s="4"/>
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
@@ -8589,14 +8597,14 @@
       <c r="AF211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="1"/>
+      <c r="A212" s="4"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="11"/>
+      <c r="D212" s="12"/>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
-      <c r="H212" s="1"/>
+      <c r="H212" s="4"/>
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
@@ -8623,14 +8631,14 @@
       <c r="AF212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="1"/>
+      <c r="A213" s="4"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="11"/>
+      <c r="D213" s="12"/>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
-      <c r="H213" s="1"/>
+      <c r="H213" s="4"/>
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
@@ -8657,14 +8665,14 @@
       <c r="AF213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="1"/>
+      <c r="A214" s="4"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="11"/>
+      <c r="D214" s="12"/>
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
-      <c r="H214" s="1"/>
+      <c r="H214" s="4"/>
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
@@ -8691,14 +8699,14 @@
       <c r="AF214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="1"/>
+      <c r="A215" s="4"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="11"/>
+      <c r="D215" s="12"/>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="3"/>
-      <c r="H215" s="1"/>
+      <c r="H215" s="4"/>
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
@@ -8725,14 +8733,14 @@
       <c r="AF215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="1"/>
+      <c r="A216" s="4"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="11"/>
+      <c r="D216" s="12"/>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
-      <c r="H216" s="1"/>
+      <c r="H216" s="4"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
@@ -8759,14 +8767,14 @@
       <c r="AF216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="1"/>
+      <c r="A217" s="4"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="11"/>
+      <c r="D217" s="12"/>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
-      <c r="H217" s="1"/>
+      <c r="H217" s="4"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
@@ -8793,14 +8801,14 @@
       <c r="AF217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="1"/>
+      <c r="A218" s="4"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="11"/>
+      <c r="D218" s="12"/>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
-      <c r="H218" s="1"/>
+      <c r="H218" s="4"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
@@ -8827,14 +8835,14 @@
       <c r="AF218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="1"/>
+      <c r="A219" s="4"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="11"/>
+      <c r="D219" s="12"/>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
-      <c r="H219" s="1"/>
+      <c r="H219" s="4"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
@@ -8861,14 +8869,14 @@
       <c r="AF219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="1"/>
+      <c r="A220" s="4"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="11"/>
+      <c r="D220" s="12"/>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
-      <c r="H220" s="1"/>
+      <c r="H220" s="4"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
@@ -8895,14 +8903,14 @@
       <c r="AF220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="1"/>
+      <c r="A221" s="4"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="11"/>
+      <c r="D221" s="12"/>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
-      <c r="H221" s="1"/>
+      <c r="H221" s="4"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
@@ -8929,14 +8937,14 @@
       <c r="AF221" s="3"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="1"/>
+      <c r="A222" s="4"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
-      <c r="D222" s="11"/>
+      <c r="D222" s="12"/>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="3"/>
-      <c r="H222" s="1"/>
+      <c r="H222" s="4"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
@@ -8963,14 +8971,14 @@
       <c r="AF222" s="3"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="1"/>
+      <c r="A223" s="4"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
-      <c r="D223" s="11"/>
+      <c r="D223" s="12"/>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
-      <c r="H223" s="1"/>
+      <c r="H223" s="4"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
@@ -8997,14 +9005,14 @@
       <c r="AF223" s="3"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="1"/>
+      <c r="A224" s="4"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="11"/>
+      <c r="D224" s="12"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
-      <c r="H224" s="1"/>
+      <c r="H224" s="4"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
@@ -9031,14 +9039,14 @@
       <c r="AF224" s="3"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="1"/>
+      <c r="A225" s="4"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
-      <c r="D225" s="11"/>
+      <c r="D225" s="12"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
-      <c r="H225" s="1"/>
+      <c r="H225" s="4"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
@@ -9065,14 +9073,14 @@
       <c r="AF225" s="3"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="1"/>
+      <c r="A226" s="4"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
-      <c r="D226" s="11"/>
+      <c r="D226" s="12"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
-      <c r="H226" s="1"/>
+      <c r="H226" s="4"/>
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
@@ -9099,14 +9107,14 @@
       <c r="AF226" s="3"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="1"/>
+      <c r="A227" s="4"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
-      <c r="D227" s="11"/>
+      <c r="D227" s="12"/>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
-      <c r="H227" s="1"/>
+      <c r="H227" s="4"/>
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
@@ -9133,14 +9141,14 @@
       <c r="AF227" s="3"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="1"/>
+      <c r="A228" s="4"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
-      <c r="D228" s="11"/>
+      <c r="D228" s="12"/>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
-      <c r="H228" s="1"/>
+      <c r="H228" s="4"/>
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
@@ -9167,14 +9175,14 @@
       <c r="AF228" s="3"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="1"/>
+      <c r="A229" s="4"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="11"/>
+      <c r="D229" s="12"/>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
-      <c r="H229" s="1"/>
+      <c r="H229" s="4"/>
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
@@ -9201,14 +9209,14 @@
       <c r="AF229" s="3"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="1"/>
+      <c r="A230" s="4"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
-      <c r="D230" s="11"/>
+      <c r="D230" s="12"/>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="G230" s="3"/>
-      <c r="H230" s="1"/>
+      <c r="H230" s="4"/>
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
@@ -9235,14 +9243,14 @@
       <c r="AF230" s="3"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="1"/>
+      <c r="A231" s="4"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
-      <c r="D231" s="11"/>
+      <c r="D231" s="12"/>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
-      <c r="H231" s="1"/>
+      <c r="H231" s="4"/>
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
@@ -9269,14 +9277,14 @@
       <c r="AF231" s="3"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="1"/>
+      <c r="A232" s="4"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="11"/>
+      <c r="D232" s="12"/>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
-      <c r="H232" s="1"/>
+      <c r="H232" s="4"/>
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
@@ -9303,14 +9311,14 @@
       <c r="AF232" s="3"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="1"/>
+      <c r="A233" s="4"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
-      <c r="D233" s="11"/>
+      <c r="D233" s="12"/>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
-      <c r="H233" s="1"/>
+      <c r="H233" s="4"/>
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
@@ -9337,14 +9345,14 @@
       <c r="AF233" s="3"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="1"/>
+      <c r="A234" s="4"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
-      <c r="D234" s="11"/>
+      <c r="D234" s="12"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
-      <c r="H234" s="1"/>
+      <c r="H234" s="4"/>
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
@@ -9371,14 +9379,14 @@
       <c r="AF234" s="3"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="1"/>
+      <c r="A235" s="4"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
-      <c r="D235" s="11"/>
+      <c r="D235" s="12"/>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
-      <c r="H235" s="1"/>
+      <c r="H235" s="4"/>
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
@@ -9405,14 +9413,14 @@
       <c r="AF235" s="3"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="1"/>
+      <c r="A236" s="4"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
-      <c r="D236" s="11"/>
+      <c r="D236" s="12"/>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
-      <c r="H236" s="1"/>
+      <c r="H236" s="4"/>
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
@@ -9439,14 +9447,14 @@
       <c r="AF236" s="3"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="1"/>
+      <c r="A237" s="4"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="11"/>
+      <c r="D237" s="12"/>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="G237" s="3"/>
-      <c r="H237" s="1"/>
+      <c r="H237" s="4"/>
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
@@ -9473,14 +9481,14 @@
       <c r="AF237" s="3"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="1"/>
+      <c r="A238" s="4"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="11"/>
+      <c r="D238" s="12"/>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="G238" s="3"/>
-      <c r="H238" s="1"/>
+      <c r="H238" s="4"/>
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
@@ -9507,14 +9515,14 @@
       <c r="AF238" s="3"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="1"/>
+      <c r="A239" s="4"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="11"/>
+      <c r="D239" s="12"/>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
-      <c r="H239" s="1"/>
+      <c r="H239" s="4"/>
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
@@ -9541,14 +9549,14 @@
       <c r="AF239" s="3"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="1"/>
+      <c r="A240" s="4"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="11"/>
+      <c r="D240" s="12"/>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
-      <c r="H240" s="1"/>
+      <c r="H240" s="4"/>
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
@@ -9575,14 +9583,14 @@
       <c r="AF240" s="3"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="1"/>
+      <c r="A241" s="4"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="11"/>
+      <c r="D241" s="12"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
-      <c r="H241" s="1"/>
+      <c r="H241" s="4"/>
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
@@ -9609,14 +9617,14 @@
       <c r="AF241" s="3"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="1"/>
+      <c r="A242" s="4"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="11"/>
+      <c r="D242" s="12"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
-      <c r="H242" s="1"/>
+      <c r="H242" s="4"/>
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
@@ -9643,14 +9651,14 @@
       <c r="AF242" s="3"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="1"/>
+      <c r="A243" s="4"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="11"/>
+      <c r="D243" s="12"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="3"/>
-      <c r="H243" s="1"/>
+      <c r="H243" s="4"/>
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
@@ -9677,14 +9685,14 @@
       <c r="AF243" s="3"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="1"/>
+      <c r="A244" s="4"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="11"/>
+      <c r="D244" s="12"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
-      <c r="H244" s="1"/>
+      <c r="H244" s="4"/>
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
@@ -9711,14 +9719,14 @@
       <c r="AF244" s="3"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="1"/>
+      <c r="A245" s="4"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="11"/>
+      <c r="D245" s="12"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
-      <c r="H245" s="1"/>
+      <c r="H245" s="4"/>
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
@@ -9745,14 +9753,14 @@
       <c r="AF245" s="3"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="1"/>
+      <c r="A246" s="4"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="11"/>
+      <c r="D246" s="12"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
-      <c r="H246" s="1"/>
+      <c r="H246" s="4"/>
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
@@ -9779,14 +9787,14 @@
       <c r="AF246" s="3"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="1"/>
+      <c r="A247" s="4"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="11"/>
+      <c r="D247" s="12"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="3"/>
-      <c r="H247" s="1"/>
+      <c r="H247" s="4"/>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
@@ -9813,14 +9821,14 @@
       <c r="AF247" s="3"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="1"/>
+      <c r="A248" s="4"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="11"/>
+      <c r="D248" s="12"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
-      <c r="H248" s="1"/>
+      <c r="H248" s="4"/>
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
@@ -9847,14 +9855,14 @@
       <c r="AF248" s="3"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="1"/>
+      <c r="A249" s="4"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="11"/>
+      <c r="D249" s="12"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="G249" s="3"/>
-      <c r="H249" s="1"/>
+      <c r="H249" s="4"/>
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
@@ -9881,14 +9889,14 @@
       <c r="AF249" s="3"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="1"/>
+      <c r="A250" s="4"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="11"/>
+      <c r="D250" s="12"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
-      <c r="H250" s="1"/>
+      <c r="H250" s="4"/>
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
@@ -9915,14 +9923,14 @@
       <c r="AF250" s="3"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="1"/>
+      <c r="A251" s="4"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="11"/>
+      <c r="D251" s="12"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="3"/>
-      <c r="H251" s="1"/>
+      <c r="H251" s="4"/>
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
@@ -10723,7 +10731,7 @@
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="8" orientation="landscape"/>
   <drawing r:id="rId5"/>
   <legacyDrawing r:id="rId6"/>
 </worksheet>
@@ -10744,112 +10752,112 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>125</v>
       </c>
+      <c r="C1" s="37" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="38" t="s">
+      <c r="A2" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="35"/>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="38" t="s">
+      <c r="A3" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="35"/>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="39" t="s">
+      <c r="A4" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="35"/>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="37" t="s">
+      <c r="A5" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="35"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="39" t="s">
+      <c r="A6" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="35"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="39" t="s">
+      <c r="A7" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="35"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="38" t="s">
+      <c r="A8" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="35"/>
     </row>
     <row r="21">
-      <c r="F21" s="40"/>
+      <c r="F21" s="41"/>
     </row>
     <row r="22">
-      <c r="K22" s="41"/>
+      <c r="K22" s="42"/>
     </row>
     <row r="23">
-      <c r="K23" s="41"/>
+      <c r="K23" s="42"/>
     </row>
     <row r="24">
-      <c r="K24" s="41"/>
+      <c r="K24" s="42"/>
     </row>
     <row r="30">
-      <c r="F30" s="40"/>
+      <c r="F30" s="41"/>
     </row>
     <row r="39">
-      <c r="F39" s="40"/>
+      <c r="F39" s="41"/>
     </row>
     <row r="48">
-      <c r="F48" s="40"/>
+      <c r="F48" s="41"/>
     </row>
     <row r="56">
-      <c r="F56" s="40"/>
+      <c r="F56" s="41"/>
     </row>
     <row r="64">
-      <c r="F64" s="40"/>
+      <c r="F64" s="41"/>
     </row>
     <row r="73">
-      <c r="F73" s="40"/>
+      <c r="F73" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="16">
